--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_direct_query_raw_table_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_direct_query_raw_table_08-24-4.xlsx
@@ -494,7 +494,8 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -511,7 +512,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -532,7 +533,8 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +551,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -570,7 +572,8 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -587,7 +590,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -608,7 +611,8 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -625,7 +629,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -646,7 +650,8 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -663,7 +668,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -684,7 +689,8 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -701,7 +707,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -722,7 +728,8 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -739,7 +746,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -760,7 +767,8 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -777,7 +785,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -798,7 +806,8 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -815,7 +824,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -836,7 +845,8 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>What is the location of the Great Wall of China? The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner Mongolia</t>
+          <t>What is the location of the Great Wall of China???
+The Great Wall of China is located in the northern part of China. It is located in the provinces of Hebei, Shanxi, and Inner</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -853,7 +863,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0), (' Mongolia', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' Great', 1.0), (' Wall', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' northern', 1.0), (' part', 1.0), (' of', 1.0), (' China', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' the', 1.0), (' provinces', 1.0), (' of', 1.0), (' He', 1.0), ('bei', 1.0), (',', 1.0), (' Shan', 1.0), ('xi', 1.0), (',', 1.0), (' and', 1.0), (' Inner', 1.0)]</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -874,7 +884,8 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -891,7 +902,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -912,7 +923,8 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -929,7 +941,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -950,24 +962,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a park in the 7th arr</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' park', 0.5), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -988,24 +1001,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a park in the 7th arr</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' park', 0.5), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1026,24 +1040,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 0.5), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0)]</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1064,24 +1079,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 0.5), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0)]</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1102,7 +1118,8 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a large park in the 7th arr</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1119,7 +1136,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' large', 1.0), (' park', 1.0), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1140,24 +1157,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars, a park in the 7th arr</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (',', 0.5), (' a', 1.0), (' park', 0.5), (' in', 1.0), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0)]</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1178,7 +1196,8 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1195,7 +1214,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1216,7 +1235,8 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Where is the Eiffel Tower located? The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of Paris</t>
+          <t>Where is the Eiffel Tower located???
+The Eiffel Tower is located in Paris, France. It is located on the Champ de Mars in the 7th arrondissement of</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1233,7 +1253,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0), (' Paris', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 1.0), (' E', 1.0), ('iff', 1.0), ('el', 1.0), (' Tower', 1.0), (' is', 1.0), (' located', 1.0), (' in', 1.0), (' Paris', 1.0), (',', 1.0), (' France', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' Champ', 1.0), (' de', 1.0), (' Mars', 1.0), (' in', 0.5), (' the', 1.0), (' ', 1.0), ('7', 1.0), ('th', 1.0), (' arr', 1.0), ('ond', 1.0), ('issement', 1.0), (' of', 1.0)]</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1254,24 +1274,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1292,24 +1313,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1330,24 +1352,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1368,24 +1391,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is also the largest city in Japan. Tokyo is located on the island of Honshu.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1406,24 +1430,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is also the largest city in Japan. Tokyo is located on the island of Honshu.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1444,24 +1469,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is also the largest city in Japan. Tokyo is located on the island of Honshu.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1482,24 +1508,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1520,24 +1547,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is located on the eastern side of the main island of Honshu. Tokyo is the largest city in</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is also the largest city in Japan. Tokyo is located on the island of Honshu.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' located', 0.5), (' on', 1.0), (' the', 1.0), (' eastern', 1.0), (' side', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.5), (' the', 1.0), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0), (' of', 1.0), (' Hon', 1.0), ('sh', 1.0), ('u', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1558,24 +1586,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1596,24 +1625,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>What is the capital city of Japan? Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on the island</t>
+          <t>What is the capital city of Japan???
+Tokyo is the capital city of Japan. It is the largest city in Japan and the largest metropolitan area in the world. Tokyo is located on</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[(' Tokyo', 1.0), (' is', 0.7773), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0), (' the', 1.0), (' island', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Tok', 1.0), ('yo', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' city', 1.0), (' of', 1.0), (' Japan', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.5), (' largest', 1.0), (' city', 1.0), (' in', 1.0), (' Japan', 1.0), (' and', 1.0), (' the', 1.0), (' largest', 1.0), (' metropolitan', 1.0), (' area', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' Tokyo', 1.0), (' is', 1.0), (' located', 1.0), (' on', 1.0)]</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -1634,28 +1664,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very sour taste. It is</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' sour', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1672,28 +1703,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very sour taste. It is</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' sour', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1710,28 +1742,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? What about the sound of a bird singing? What about the feeling of a warm summer breeze? What about the</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very strong taste. It is</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.01941082999110222</v>
+        <v>0.25</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8768692016601562</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G34" t="n">
-        <v>1.394994616508484</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' What', 0.3486), (' about', 1.0), (' the', 1.0), (' sound', 1.0), (' of', 1.0), (' a', 1.0), (' bird', 1.0), (' singing', 0.5), ('?', 1.0), (' What', 1.0), (' about', 1.0), (' the', 1.0), (' feeling', 0.5), (' of', 1.0), (' a', 1.0), (' warm', 1.0), (' summer', 1.0), (' breeze', 1.0), ('?', 1.0), (' What', 1.0), (' about', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' strong', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1748,28 +1781,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very strong taste. It is</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' strong', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1786,28 +1820,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very strong taste. It is</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' strong', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1824,28 +1859,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a citrus fruit that is very sour. It is used in many different</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.0833333283662796</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9205074310302734</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.059351325035095</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' citrus', 0.5), (' fruit', 1.0), (' that', 1.0), (' is', 1.0), (' very', 0.3333), (' sour', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' used', 0.5), (' in', 1.0), (' many', 1.0), (' different', 1.0)]</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1862,28 +1898,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it hot? Is it cold? Is it</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very strong taste. It is</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.25</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5423979759216309</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' hot', 0.5), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' cold', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' strong', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1900,28 +1937,29 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? What about the smell of a rose? What about the sound of a bird chirping? These are all examples of sensory experiences that we can describe,</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a very sour taste. It is a very strong taste. It is</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01941082999110222</v>
+        <v>0.25</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8768692016601562</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G39" t="n">
-        <v>1.394994616508484</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[(' What', 0.2227), (' about', 1.0), (' the', 1.0), (' smell', 1.0), (' of', 1.0), (' a', 1.0), (' rose', 1.0), ('?', 1.0), (' What', 0.3486), (' about', 1.0), (' the', 1.0), (' sound', 1.0), (' of', 1.0), (' a', 1.0), (' bird', 1.0), (' chir', 0.5), ('ping', 1.0), ('?', 1.0), (' These', 1.0), (' are', 1.0), (' all', 1.0), (' examples', 1.0), (' of', 1.0), (' sensory', 1.0), (' experiences', 1.0), (' that', 1.0), (' we', 1.0), (' can', 1.0), (' describe', 1.0), (',', 0.5)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 0.5), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' strong', 0.5), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1938,28 +1976,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it hot? Is it cold? Is it</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a citrus fruit that is very sour. It is used in many different</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.0833333283662796</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9205074310302734</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.059351325035095</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' hot', 0.5), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' cold', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' citrus', 0.5), (' fruit', 1.0), (' that', 1.0), (' is', 1.0), (' very', 0.3333), (' sour', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' used', 0.5), (' in', 1.0), (' many', 1.0), (' different', 1.0)]</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1976,28 +2015,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>How would you describe the taste of a lemon? Is it sour? Is it bitter? Is it sweet? Is it salty? Is it spicy? Is it tangy? Is it tart? Is</t>
+          <t>How would you describe the taste of a lemon???
+I would describe the taste of a lemon as a sour taste. It is a citrus fruit that is yellow in color. It is a very popular</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3886499404907227</v>
+        <v>0.06477499008178711</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9689884781837463</v>
+        <v>0.9128096699714661</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5423979759216309</v>
+        <v>1.255175709724426</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[(' Is', 0.7773), (' it', 1.0), (' sour', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' bitter', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' sweet', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' salty', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' spicy', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tang', 0.5), ('y', 1.0), ('?', 1.0), (' Is', 1.0), (' it', 1.0), (' tart', 1.0), ('?', 1.0), (' Is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 1.0), (' taste', 1.0), (' of', 1.0), (' a', 1.0), (' lemon', 1.0), (' as', 1.0), (' a', 1.0), (' sour', 1.0), (' taste', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' citrus', 0.5), (' fruit', 1.0), (' that', 1.0), (' is', 1.0), (' yellow', 0.3333), (' in', 1.0), (' color', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 0.5), (' very', 1.0), (' popular', 0.7773)]</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2014,24 +2054,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2052,24 +2094,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2090,24 +2134,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2128,24 +2174,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2166,24 +2214,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp. It’s a perfect day for a picnic or a walk in the park</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.1113500744104385</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9294435381889343</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6810534000396729</v>
+        <v>-0</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' perfect', 1.0), (' day', 1.0), (' for', 1.0), (' a', 1.0), (' picnic', 1.0), (' or', 1.0), (' a', 1.0), (' walk', 0.5), (' in', 1.0), (' the', 1.0), (' park', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2204,24 +2254,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2242,24 +2294,26 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2280,24 +2334,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The sky is blue, the sun is shining, and the air is crisp. It’s a perfect day for a picnic or a hike in the woods</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.1113500744104385</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9294435381889343</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6810534000396729</v>
+        <v>-0</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' sky', 0.2227), (' is', 1.0), (' blue', 1.0), (',', 1.0), (' the', 1.0), (' sun', 1.0), (' is', 1.0), (' shining', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' air', 1.0), (' is', 1.0), (' crisp', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' perfect', 1.0), (' day', 1.0), (' for', 1.0), (' a', 1.0), (' picnic', 1.0), (' or', 1.0), (' a', 1.0), (' hike', 0.5), (' in', 1.0), (' the', 1.0), (' woods', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -2318,24 +2374,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -2356,24 +2414,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>What is the best way to describe the weather on a clear day? The weather is clear. What is the best way to describe the weather on a cloudy day? The weather is cloudy. What is the best way to</t>
+          <t>What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day???
+What is the best way to describe the weather on a clear day??</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.7772998809814453</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9916375279426575</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1958244144916534</v>
+        <v>-0</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' weather', 0.7773), (' is', 1.0), (' clear', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' cloudy', 1.0), (' day', 1.0), ('?', 1.0), (' The', 1.0), (' weather', 1.0), (' is', 1.0), (' cloudy', 1.0), ('.', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' best', 1.0), (' way', 1.0), (' to', 1.0), (' describe', 1.0), (' the', 1.0), (' weather', 1.0), (' on', 1.0), (' a', 1.0), (' clear', 1.0), (' day', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -2394,24 +2454,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. It is a very nice feeling.://www.://www</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 0.7773), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -2432,24 +2493,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. It is a very nice feeling.://www.://www</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 0.7773), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -2470,24 +2532,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that you want to experience again and again. And that’s exactly how you should feel</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. It is a very nice feeling.://www.://www</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.1135458499193192</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9300487637519836</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9931774139404297</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), (' you', 0.3486), (' want', 1.0), (' to', 1.0), (' experience', 1.0), (' again', 0.5), (' and', 1.0), (' again', 1.0), ('.', 1.0), (' And', 1.0), (' that', 1.0), ('’s', 1.0), (' exactly', 1.0), (' how', 1.0), (' you', 1.0), (' should', 1.0), (' feel', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 0.7773), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -2508,24 +2571,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? Soft, smooth, and luxurious, right? Now imagine that same feeling on your skin. That’s the feeling you get when you use a velvet body</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. It is a very nice feeling to touch velvet. It is a very nice feeling</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1743225604295731</v>
+        <v>0.1113500744104385</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9434345960617065</v>
+        <v>0.9294435381889343</v>
       </c>
       <c r="G55" t="n">
-        <v>0.713941216468811</v>
+        <v>0.6810534000396729</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[(' Soft', 0.3486), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), (',', 1.0), (' right', 1.0), ('?', 1.0), (' Now', 0.5), (' imagine', 1.0), (' that', 1.0), (' same', 1.0), (' feeling', 1.0), (' on', 1.0), (' your', 1.0), (' skin', 1.0), ('.', 1.0), (' That', 1.0), ('’s', 1.0), (' the', 1.0), (' feeling', 1.0), (' you', 1.0), (' get', 1.0), (' when', 1.0), (' you', 1.0), (' use', 1.0), (' a', 1.0), (' velvet', 1.0), (' body', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), (' to', 0.2227), (' touch', 1.0), (' velvet', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0)]</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -2546,24 +2610,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe it as soft and smooth. It is a very nice feeling.://www.://www.://</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.25</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 0.5), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0)]</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -2584,24 +2649,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. It is a very nice feeling.://www.://www</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 0.7773), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -2622,24 +2688,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that we all know and love.</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe the feeling of touching velvet as soft and smooth. It is a very nice feeling.://www.://www</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.07727444916963577</v>
+        <v>0.3886499404907227</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9181941747665405</v>
+        <v>0.9689884781837463</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8686517477035522</v>
+        <v>0.5423979759216309</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), (' we', 0.1821), (' all', 1.0), (' know', 1.0), (' and', 1.0), (' love', 1.0), ('.', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' the', 0.5), (' feeling', 1.0), (' of', 1.0), (' touching', 1.0), (' velvet', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 0.7773), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -2660,24 +2727,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that you want to experience over and over again. And that’s exactly what you get</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe it as soft and smooth. It is a very nice feeling.://www.://www.://</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.05677292495965958</v>
+        <v>0.25</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9088063836097717</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G59" t="n">
-        <v>1.339751005172729</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), (' you', 0.3486), (' want', 1.0), (' to', 1.0), (' experience', 1.0), (' over', 0.5), (' and', 1.0), (' over', 1.0), (' again', 1.0), ('.', 1.0), (' And', 1.0), (' that', 1.0), ('’s', 1.0), (' exactly', 1.0), (' what', 0.5), (' you', 1.0), (' get', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 0.5), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0)]</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -2698,24 +2766,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe it as soft and smooth. It is a very nice feeling.://www.://www.://</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.25</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8464494943618774</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 0.5), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 0.5), (' It', 1.0), (' is', 1.0), (' a', 1.0), (' very', 1.0), (' nice', 1.0), (' feeling', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0)]</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -2736,24 +2805,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>How would you describe the feeling of touching velvet? It’s soft, smooth, and luxurious. It’s a feeling that’s hard to describe, but it’s one that’s often associated with luxury and</t>
+          <t>How would you describe the feeling of touching velvet???
+I would describe it as soft and smooth.
+I would describe it as soft and smooth.://www.://www.</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2697143256664276</v>
+        <v>0.125</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9572604894638062</v>
+        <v>0.9330329895019531</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8464494943618774</v>
+        <v>1.039720773696899</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[(' It', 0.6514), ('’s', 1.0), (' soft', 1.0), (',', 1.0), (' smooth', 1.0), (',', 1.0), (' and', 1.0), (' luxurious', 1.0), ('.', 1.0), (' It', 1.0), ('’s', 1.0), (' a', 1.0), (' feeling', 1.0), (' that', 1.0), ('’s', 0.6514), (' hard', 1.0), (' to', 1.0), (' describe', 1.0), (',', 1.0), (' but', 1.0), (' it', 1.0), ('’s', 1.0), (' one', 1.0), (' that', 1.0), ('’s', 0.6357), (' often', 1.0), (' associated', 1.0), (' with', 1.0), (' luxury', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 0.5), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.\n', 0.5), ('I', 1.0), (' would', 1.0), (' describe', 1.0), (' it', 1.0), (' as', 1.0), (' soft', 1.0), (' and', 1.0), (' smooth', 1.0), ('.', 0.5), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -2774,28 +2845,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2812,28 +2885,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2850,28 +2925,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2888,28 +2965,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2926,28 +3005,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2964,28 +3045,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3002,28 +3085,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3040,28 +3125,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3078,28 +3165,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who was the first president of the United States? George Washington. Who</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[(' George', 0.3486), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' George', 1.0), (' Washington', 1.0), ('.', 1.0), (' Who', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3116,28 +3205,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Who was the first president of the United States? What was the first state admitted to the Union? What is the capital of the United States? What is the name of the highest mountain in the United</t>
+          <t>Who was the first president of the United States???
+Who was the first president of the United States???
+George Washington was the first president of the United States. He was elected in 1789</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.5062980651855469</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9775677919387817</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4750606417655945</v>
+        <v>-0</v>
       </c>
       <c r="H71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[(' What', 0.6514), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' state', 1.0), (' admitted', 1.0), (' to', 1.0), (' the', 1.0), (' Union', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' capital', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 0.7773), (' of', 1.0), (' the', 1.0), (' highest', 1.0), (' mountain', 1.0), (' in', 1.0), (' the', 1.0), (' United', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('??', 1.0), ('?\n', 1.0), ('George', 1.0), (' Washington', 1.0), (' was', 1.0), (' the', 1.0), (' first', 1.0), (' president', 1.0), (' of', 1.0), (' the', 1.0), (' United', 1.0), (' States', 1.0), ('.', 1.0), (' He', 1.0), (' was', 1.0), (' elected', 1.0), (' in', 1.0), (' ', 1.0), ('178', 1.0), ('9', 1.0)]</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3154,30 +3245,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4829698204994202</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9760318994522095</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3515059649944305</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3194,30 +3285,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.4829698204994202</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9760318994522095</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3515059649944305</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3234,30 +3325,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Jane Austen
-What is the name of the main character in 'Pride and Prejudice'? Elizabeth Bennet
-What is the name of</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen was the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.2585151195526123</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9559082388877869</v>
+        <v>0.9511682391166687</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3497195243835449</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[(' Jane', 0.2585), (' Aust', 1.0), ('en', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' Elizabeth', 1.0), (' Benn', 1.0), ('et', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' was', 0.2227), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3274,30 +3365,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.4829698204994202</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9760318994522095</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3515059649944305</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3314,28 +3405,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2585151195526123</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9559082388877869</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3497195243835449</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3352,30 +3445,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Jane Austen
-What is the name of the main character in 'Pride and Prejudice'? Elizabeth Bennet
-What is the name of</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.2585151195526123</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9559082388877869</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3497195243835449</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[(' Jane', 0.2585), (' Aust', 1.0), ('en', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' Elizabeth', 1.0), (' Benn', 1.0), ('et', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3392,28 +3485,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2585151195526123</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9559082388877869</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3497195243835449</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3430,30 +3525,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? Who is the author of 'Pride and Prejudice'?
-Who is the author of 'Pride and Prejudice'?
-Jane Aust</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen was the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.4829698204994202</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9760318994522095</v>
+        <v>0.9511682391166687</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3515059649944305</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="H79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[(' Who', 0.483), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' was', 0.2227), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3470,28 +3565,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.2585151195526123</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F80" t="n">
-        <v>0.9559082388877869</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3497195243835449</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3508,28 +3605,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Who is the author of 'Pride and Prejudice'? What is the name of the main character in 'Pride and Prejudice'? What is the name of the main character in 'Pride and</t>
+          <t>Who is the author of 'Pride and Prejudice'???
+Who is the author of 'Pride and Prejudice'???
+Jane Austen is the author of Pride and Prejudice. She</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.2585151195526123</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9559082388877869</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3497195243835449</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[(' What', 0.2585), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'?", 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' main', 1.0), (' character', 1.0), (' in', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' is', 1.0), (' the', 1.0), (' author', 1.0), (' of', 1.0), (" '", 1.0), ('P', 1.0), ('ride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ("'", 1.0), ('??', 1.0), ('?\n', 1.0), ('Jane', 1.0), (' Aust', 1.0), ('en', 1.0), (' is', 0.7773), (' the', 1.0), (' author', 1.0), (' of', 1.0), (' Pride', 1.0), (' and', 1.0), (' Pre', 1.0), ('jud', 1.0), ('ice', 1.0), ('.', 1.0), (' She', 1.0)]</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3546,28 +3645,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Post by The Cat » Mon Jul 30, 2007 12:59 pm
+The Mona Lisa</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.209648922085762</v>
+        <v>4.392413029563613e-05</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.7157424688339233</v>
       </c>
       <c r="G82" t="n">
-        <v>1.042273879051208</v>
+        <v>2.55106258392334</v>
       </c>
       <c r="H82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 0.3486), (' by', 1.0), (' The', 1.0), (' Cat', 0.3333), (' »', 1.0), (' Mon', 0.5378), (' Jul', 0.2913), (' ', 1.0), ('30', 0.1667), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), (' ', 1.0), ('12', 0.3333), (':', 1.0), ('59', 0.0667), (' pm', 1.0), ('\n', 1.0), ('The', 0.6514), (' Mona', 1.0), (' Lisa', 1.0)]</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3584,28 +3686,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Post by The Great Hippo » 2018-04-10 02:33pm
+The Mona</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.209648922085762</v>
+        <v>2.53919324677554e-06</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.6508634090423584</v>
       </c>
       <c r="G83" t="n">
-        <v>1.042273879051208</v>
+        <v>2.292897939682007</v>
       </c>
       <c r="H83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 0.3486), (' by', 1.0), (' The', 1.0), (' Great', 0.3333), (' Hipp', 0.6514), ('o', 1.0), (' »', 1.0), (' ', 0.5), ('201', 1.0), ('8', 1.0), ('-', 1.0), ('04', 0.1892), ('-', 1.0), ('10', 0.1295), (' ', 1.0), ('02', 0.1429), (':', 1.0), ('33', 0.0192), ('pm', 1.0), ('\n', 1.0), ('The', 1.0), (' Mona', 1.0)]</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3622,28 +3727,33 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? That’s a question that has been debated for centuries. Some say it</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.2710018157958984</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9574124813079834</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5631920099258423</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' That', 0.3486), ('’s', 1.0), (' a', 1.0), (' question', 1.0), (' that', 1.0), (' has', 1.0), (' been', 1.0), (' debated', 1.0), (' for', 1.0), (' centuries', 1.0), ('.', 1.0), (' Some', 1.0), (' say', 1.0), (' it', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 0.6514), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3660,28 +3770,33 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa Gherardini, the wife of a Florentine merchant. When was</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.02783751860260963</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8874713778495789</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G85" t="n">
-        <v>1.374200582504272</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0), ('her', 1.0), ('ard', 1.0), ('ini', 1.0), (',', 1.0), (' the', 0.5), (' wife', 1.0), (' of', 1.0), (' a', 1.0), (' Flo', 1.0), ('rent', 1.0), ('ine', 1.0), (' merchant', 1.0), ('.', 1.0), (' When', 0.5), (' was', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 0.6514), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3698,28 +3813,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Post by The Dude » Thu Jan 10, 2008 12:52 pm
+The Mona Lisa</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.209648922085762</v>
+        <v>1.62962078320561e-05</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.6924730539321899</v>
       </c>
       <c r="G86" t="n">
-        <v>1.042273879051208</v>
+        <v>2.528167247772217</v>
       </c>
       <c r="H86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 0.3486), (' by', 1.0), (' The', 1.0), (' Dude', 0.3333), (' »', 1.0), (' Thu', 0.2), (' Jan', 0.5756), (' ', 1.0), ('10', 0.3886), (',', 1.0), (' ', 1.0), ('200', 1.0), ('8', 1.0), (' ', 1.0), ('12', 0.3333), (':', 1.0), ('52', 0.0188), (' pm', 1.0), ('\n', 1.0), ('The', 0.5), (' Mona', 1.0), (' Lisa', 1.0)]</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3736,28 +3854,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa Gherardini, wife of Francesco del Giocondo. When was the</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Post by The Dude » Tue Jan 22, 2008 10:03 pm
+I was reading</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.04327619820833206</v>
+        <v>1.264741626982868e-06</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9006201028823853</v>
+        <v>0.6359164118766785</v>
       </c>
       <c r="G87" t="n">
-        <v>1.223451375961304</v>
+        <v>3.082245826721191</v>
       </c>
       <c r="H87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0), ('her', 1.0), ('ard', 1.0), ('ini', 1.0), (',', 1.0), (' wife', 0.5), (' of', 1.0), (' Francesco', 1.0), (' del', 1.0), (' Gio', 1.0), ('cond', 1.0), ('o', 1.0), ('.', 1.0), (' When', 0.7773), (' was', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 0.3486), (' by', 1.0), (' The', 1.0), (' Dude', 0.3333), (' »', 1.0), (' Tue', 0.2), (' Jan', 0.3678), (' ', 1.0), ('22', 0.2), (',', 1.0), (' ', 1.0), ('200', 1.0), ('8', 1.0), (' ', 1.0), ('10', 0.3333), (':', 1.0), ('03', 0.0256), (' pm', 1.0), ('\n', 1.0), ('I', 0.7773), (' was', 0.5), (' reading', 0.2227)]</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3774,28 +3895,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is, no one knows. The Mona Lisa’s smile is</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Post by The Cat » Tue Jan 08, 2008 11:49 pm
+I've been</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0922161266207695</v>
+        <v>7.692206054343842e-06</v>
       </c>
       <c r="F88" t="n">
-        <v>0.9236205220222473</v>
+        <v>0.6753594875335693</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7852399349212646</v>
+        <v>2.653378486633301</v>
       </c>
       <c r="H88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (',', 0.1821), (' no', 1.0), (' one', 1.0), (' knows', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 0.3486), (' by', 1.0), (' The', 1.0), (' Cat', 0.3333), (' »', 1.0), (' Tue', 0.1541), (' Jan', 0.3678), (' ', 1.0), ('08', 0.8024), (',', 1.0), (' ', 1.0), ('200', 1.0), ('8', 1.0), (' ', 1.0), ('11', 0.25), (':', 1.0), ('49', 0.0256), (' pm', 1.0), ('\n', 1.0), ('I', 0.6514), ("'ve", 0.3486), (' been', 1.0)]</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3812,28 +3936,33 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.209648922085762</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G89" t="n">
-        <v>1.042273879051208</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 0.6514), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3850,28 +3979,33 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci, of course. But who painted the Mona Lisa’s smile? The answer is: no one. The Mona Lisa’s smile is a</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.209648922085762</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9492554068565369</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G90" t="n">
-        <v>1.042273879051208</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), (',', 0.7773), (' of', 1.0), (' course', 1.0), ('.', 1.0), (' But', 1.0), (' who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), ('?', 1.0), (' The', 0.6514), (' answer', 1.0), (' is', 1.0), (':', 0.6357), (' no', 0.6514), (' one', 1.0), ('.', 1.0), (' The', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('’s', 1.0), (' smile', 1.0), (' is', 1.0), (' a', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 0.6514), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -3888,28 +4022,33 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Who painted the Mona Lisa? Leonardo da Vinci. What is the Mona Lisa? A portrait of Lisa Gherardini, the wife of a Florentine merchant. Where is</t>
+          <t>Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who painted the Mona Lisa???
+Who</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.02783751860260963</v>
+        <v>0.6513549089431763</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8874713778495789</v>
+        <v>0.9858115911483765</v>
       </c>
       <c r="G91" t="n">
-        <v>1.374200582504272</v>
+        <v>0.279236227273941</v>
       </c>
       <c r="H91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[(' Leonardo', 1.0), (' da', 1.0), (' Vinci', 1.0), ('.', 0.2227), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('?', 1.0), (' A', 1.0), (' portrait', 0.5), (' of', 1.0), (' Lisa', 1.0), (' G', 1.0), ('her', 1.0), ('ard', 1.0), ('ini', 1.0), (',', 1.0), (' the', 0.5), (' wife', 1.0), (' of', 1.0), (' a', 1.0), (' Flo', 1.0), ('rent', 1.0), ('ine', 1.0), (' merchant', 1.0), ('.', 1.0), (' Where', 0.5), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 0.6514), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0), (' painted', 1.0), (' the', 1.0), (' Mona', 1.0), (' Lisa', 1.0), ('??', 1.0), ('?\n', 1.0), ('Who', 1.0)]</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -3926,24 +4065,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>0.9858115911483765</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -3964,24 +4104,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0.9858115911483765</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -4002,24 +4143,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -4040,24 +4182,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9858115911483765</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -4078,24 +4221,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -4116,24 +4260,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J97" t="n">
@@ -4154,24 +4299,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -4192,24 +4338,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9858115911483765</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H99" t="b">
         <v>0</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -4230,24 +4377,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color? What is your favorite color?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.6513549089431763</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>0.9858115911483765</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>0.279236227273941</v>
+        <v>-0</v>
       </c>
       <c r="H100" t="b">
         <v>0</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 0.6514), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' color', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -4268,24 +4416,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>What is your favorite color? What is your favorite food? What is your favorite animal? What is your favorite sport? What is your favorite movie? What is your favorite book?</t>
+          <t>What is your favorite color???
+I love the color blue. I love the color blue. I love the color blue. I love the color blue. I love the color blue</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.3486451208591461</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>0.9654862880706787</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3673676252365112</v>
+        <v>-0</v>
       </c>
       <c r="H101" t="b">
         <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' food', 0.3486), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' animal', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' sport', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' movie', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' your', 1.0), (' favorite', 1.0), (' book', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0), ('.', 1.0), (' I', 1.0), (' love', 1.0), (' the', 1.0), (' color', 1.0), (' blue', 1.0)]</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -4306,24 +4455,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. To do what you want to do and to be who you want to</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.5</v>
+        <v>0.1265745162963867</v>
       </c>
       <c r="F102" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9334223866462708</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.168207883834839</v>
       </c>
       <c r="H102" t="b">
         <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.6514), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' To', 1.0), (' do', 0.7773), (' what', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0), (' do', 1.0), (' and', 0.5), (' to', 0.5), (' be', 1.0), (' who', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0)]</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -4344,24 +4494,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. To do what you want to do and to be who you want to</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.5</v>
+        <v>0.1265745162963867</v>
       </c>
       <c r="F103" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9334223866462708</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.168207883834839</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.6514), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' To', 1.0), (' do', 0.7773), (' what', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0), (' do', 1.0), (' and', 0.5), (' to', 0.5), (' be', 1.0), (' who', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0)]</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -4382,24 +4533,26 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+What do you think of the meaning of life???
+Post by The Great One » Wed Jan 02, 2013 12:38</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.5</v>
+        <v>5.015465649194084e-05</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.7189141511917114</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.73161792755127</v>
       </c>
       <c r="H104" t="b">
         <v>0</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 1.0), (' by', 1.0), (' The', 1.0), (' Great', 1.0), (' One', 1.0), (' »', 1.0), (' Wed', 0.2), (' Jan', 0.6042), (' ', 1.0), ('02', 0.25), (',', 1.0), (' ', 1.0), ('201', 1.0), ('3', 1.0), (' ', 1.0), ('12', 0.1429), (':', 1.0), ('38', 0.0333)]</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -4420,24 +4573,26 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+What do you think of the meaning of life???
+Post by The Great One » 2008-05-23, 11:37</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5</v>
+        <v>1.725285983411595e-06</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.6425328850746155</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3465735912322998</v>
+        <v>2.401682376861572</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 1.0), (' by', 1.0), (' The', 1.0), (' Great', 1.0), (' One', 1.0), (' »', 1.0), (' ', 0.2), ('200', 0.2227), ('8', 0.5), ('-', 1.0), ('05', 0.2689), ('-', 1.0), ('23', 0.0476), (',', 1.0), (' ', 1.0), ('11', 0.2256), (':', 1.0), ('37', 0.0769)]</t>
         </is>
       </c>
       <c r="J105" t="n">
@@ -4458,24 +4613,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. To live it with no regrets. To live it with no fear.</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5</v>
+        <v>0.03230417519807816</v>
       </c>
       <c r="F106" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.8918845057487488</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.9481958150863647</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.6514), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' To', 1.0), (' live', 0.2227), (' it', 1.0), (' with', 0.2227), (' no', 1.0), (' regrets', 1.0), ('.', 1.0), (' To', 1.0), (' live', 1.0), (' it', 1.0), (' with', 1.0), (' no', 1.0), (' fear', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -4496,24 +4652,26 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+What do you think of the meaning of life???
+Post by The Great One » 2010-07-01 11:08pm</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.5</v>
+        <v>1.194892888634058e-06</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.634713351726532</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.665082097053528</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 1.0), (' by', 1.0), (' The', 1.0), (' Great', 1.0), (' One', 1.0), (' »', 1.0), (' ', 0.2), ('201', 0.7773), ('0', 1.0), ('-', 1.0), ('07', 0.1111), ('-', 1.0), ('01', 0.0625), (' ', 1.0), ('11', 0.1429), (':', 1.0), ('08', 0.0222), ('pm', 1.0)]</t>
         </is>
       </c>
       <c r="J107" t="n">
@@ -4534,24 +4692,26 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is the meaning of life? What is</t>
+          <t>What do you think of the meaning of life???
+What do you think of the meaning of life???
+Post by The Great One » Mon Jan 14, 2008 12:12</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.5</v>
+        <v>0.0001068534256774001</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.7372695207595825</v>
       </c>
       <c r="G108" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.930818557739258</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 0.5), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' is', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('??', 1.0), ('?\n', 1.0), ('Post', 1.0), (' by', 1.0), (' The', 1.0), (' Great', 1.0), (' One', 1.0), (' »', 1.0), (' Mon', 0.2), (' Jan', 0.3678), (' ', 1.0), ('14', 0.25), (',', 1.0), (' ', 1.0), ('200', 1.0), ('8', 1.0), (' ', 1.0), ('12', 0.25), (':', 1.0), ('12', 0.0667)]</t>
         </is>
       </c>
       <c r="J108" t="n">
@@ -4572,24 +4732,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. To do what you want to do and not what others want you to</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.5</v>
+        <v>0.1265745162963867</v>
       </c>
       <c r="F109" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9334223866462708</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.168207883834839</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.6514), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' To', 1.0), (' do', 0.7773), (' what', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0), (' do', 1.0), (' and', 0.5), (' not', 0.5), (' what', 1.0), (' others', 1.0), (' want', 1.0), (' you', 1.0), (' to', 1.0)]</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -4610,24 +4771,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. To do what you want to do and not what others want you to</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.5</v>
+        <v>0.1265745162963867</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9334223866462708</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.168207883834839</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.6514), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' To', 1.0), (' do', 0.7773), (' what', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0), (' do', 1.0), (' and', 0.5), (' not', 0.5), (' what', 1.0), (' others', 1.0), (' want', 1.0), (' you', 1.0), (' to', 1.0)]</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -4648,24 +4810,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life? What do you think of the meaning of life?</t>
+          <t>What do you think of the meaning of life???
+I think that the meaning of life is to live it to the fullest. To do what you want to do, and to be who you want</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.5</v>
+        <v>0.1265745162963867</v>
       </c>
       <c r="F111" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9334223866462708</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3465735912322998</v>
+        <v>1.168207883834839</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' do', 0.5), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0), (' What', 1.0), (' do', 1.0), (' you', 1.0), (' think', 1.0), (' of', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 0.6514), (' think', 1.0), (' that', 1.0), (' the', 1.0), (' meaning', 1.0), (' of', 1.0), (' life', 1.0), (' is', 1.0), (' to', 1.0), (' live', 1.0), (' it', 1.0), (' to', 1.0), (' the', 1.0), (' fullest', 1.0), ('.', 1.0), (' To', 1.0), (' do', 0.7773), (' what', 1.0), (' you', 1.0), (' want', 1.0), (' to', 1.0), (' do', 1.0), (',', 0.5), (' and', 1.0), (' to', 1.0), (' be', 1.0), (' who', 0.5), (' you', 1.0), (' want', 1.0)]</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -4686,24 +4849,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about it since I was a child. I have been thinking about it</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G112" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 0.5), (' since', 1.0), (' I', 1.0), (' was', 1.0), (' a', 1.0), (' child', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -4724,24 +4888,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about it since I was a child. I have been thinking about it</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G113" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 0.5), (' since', 1.0), (' I', 1.0), (' was', 1.0), (' a', 1.0), (' child', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -4762,24 +4927,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about it since I was a child. I have been thinking about it</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G114" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 0.5), (' since', 1.0), (' I', 1.0), (' was', 1.0), (' a', 1.0), (' child', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -4800,24 +4966,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about the end of the world. I have been thinking about the end</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G115" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 0.5), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 1.0), (' end', 1.0)]</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -4838,24 +5005,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about the end of the world. I have been thinking about the end</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G116" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 0.5), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 1.0), (' end', 1.0)]</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -4876,24 +5044,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about the end of the world. I have been thinking about the end</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G117" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 0.5), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 1.0), (' end', 1.0)]</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -4914,24 +5083,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about it since I was a child. I have been thinking about it</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G118" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 0.5), (' since', 1.0), (' I', 1.0), (' was', 1.0), (' a', 1.0), (' child', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -4952,24 +5122,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about it since I was a child. I have been thinking about it</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G119" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 0.5), (' since', 1.0), (' I', 1.0), (' was', 1.0), (' a', 1.0), (' child', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -4990,24 +5161,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about the end of the world. I have been thinking about the end</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G120" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 0.5), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' the', 1.0), (' end', 1.0)]</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -5028,24 +5200,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>What comes after the end? The end of the world, the end of the universe, the end of time, the end of everything? What comes after the end? The end</t>
+          <t>What comes after the end???
+I have been thinking about this for a while now. I have been thinking about it since I was a child. I have been thinking about it</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G121" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H121" t="b">
         <v>0</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' world', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' the', 1.0), (' universe', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' time', 1.0), (',', 1.0), (' the', 1.0), (' end', 1.0), (' of', 1.0), (' everything', 1.0), ('?', 1.0), (' What', 1.0), (' comes', 1.0), (' after', 1.0), (' the', 1.0), (' end', 1.0), ('?', 1.0), (' The', 1.0), (' end', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' this', 1.0), (' for', 1.0), (' a', 1.0), (' while', 1.0), (' now', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 0.5), (' since', 1.0), (' I', 1.0), (' was', 1.0), (' a', 1.0), (' child', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' thinking', 1.0), (' about', 1.0), (' it', 1.0)]</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -5066,24 +5239,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.9511682391166687</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H122" t="b">
         <v>1</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -5104,24 +5279,26 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9511682391166687</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H123" t="b">
         <v>1</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -5142,24 +5319,26 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H124" t="b">
         <v>1</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -5180,24 +5359,26 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H125" t="b">
         <v>1</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -5218,24 +5399,26 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H126" t="b">
         <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -5256,24 +5439,26 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H127" t="b">
         <v>1</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -5294,24 +5479,26 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H128" t="b">
         <v>1</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -5332,24 +5519,26 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.3886499404907227</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>0.9689884781837463</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.5423979759216309</v>
+        <v>-0</v>
       </c>
       <c r="H129" t="b">
         <v>1</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' continents', 0.5), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -5370,24 +5559,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven. The seven continents are Africa, Antarctica, Asia, Australia, Europe, North America, and South America. Each continent has its</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.1943249702453613</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>0.9468567371368408</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8889715671539307</v>
+        <v>-0</v>
       </c>
       <c r="H130" t="b">
         <v>1</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), ('.', 0.7773), (' The', 1.0), (' seven', 0.5), (' continents', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 0.5), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -5408,24 +5599,26 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>How many continents are there on Earth? The answer is seven: Africa, Antarctica, Asia, Australia/Oceania, Europe, North America, and South America. Each continent has its own</t>
+          <t>How many continents are there on Earth???
+There are seven continents on Earth. They are Africa, Antarctica, Asia, Australia, Europe, North America, and South America.
+How many continents</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.2227001488208771</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>0.9511682391166687</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0.334479808807373</v>
+        <v>-0</v>
       </c>
       <c r="H131" t="b">
         <v>1</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' answer', 1.0), (' is', 1.0), (' seven', 1.0), (':', 0.2227), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), ('/O', 1.0), ('ce', 1.0), ('ania', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' Each', 1.0), (' continent', 1.0), (' has', 1.0), (' its', 1.0), (' own', 1.0)]</t>
+          <t>[('?\n', 1.0), ('There', 1.0), (' are', 1.0), (' seven', 1.0), (' continents', 1.0), (' on', 1.0), (' Earth', 1.0), ('.', 1.0), (' They', 1.0), (' are', 1.0), (' Africa', 1.0), (',', 1.0), (' Antarctica', 1.0), (',', 1.0), (' Asia', 1.0), (',', 1.0), (' Australia', 1.0), (',', 1.0), (' Europe', 1.0), (',', 1.0), (' North', 1.0), (' America', 1.0), (',', 1.0), (' and', 1.0), (' South', 1.0), (' America', 1.0), ('.\n', 1.0), ('How', 1.0), (' many', 1.0), (' continents', 1.0)]</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -5446,24 +5639,26 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F132" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H132" t="b">
         <v>1</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 0.5), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -5484,24 +5679,27 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius.
+The boiling point of water is</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F133" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H133" t="b">
         <v>1</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.\n', 0.5), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -5522,24 +5720,27 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius.
+Q: What is the boiling point of water in Celsius???
+What is the boiling point</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F134" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H134" t="b">
         <v>1</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.\n', 0.5), ('Q', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -5560,24 +5761,27 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius.
+The boiling point of water is</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F135" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H135" t="b">
         <v>1</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.\n', 0.5), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -5598,25 +5802,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas.
-What is the boiling</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 100 degrees Celsius. The boiling point of water is</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F136" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H136" t="b">
         <v>1</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 0.5), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -5637,24 +5841,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 100 degrees Celsius. The boiling point of water is</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H137" t="b">
         <v>1</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 0.5), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -5675,25 +5880,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas.
-What is the boiling</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 100 degrees Celsius. The boiling point of water is</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F138" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G138" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H138" t="b">
         <v>1</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 0.5), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -5714,24 +5919,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius. The boiling point of water is 100 degrees Celsius. The boiling point of water is</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F139" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G139" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H139" t="b">
         <v>1</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 0.5), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -5752,25 +5958,27 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. This is the temperature at which water changes from a liquid to a gas.
-What is the boiling</t>
+          <t>What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius.
+Q: What is the boiling point of water in Celsius???
+What is the boiling point</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.5</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F140" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H140" t="b">
         <v>1</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' This', 0.5), (' is', 1.0), (' the', 1.0), (' temperature', 1.0), (' at', 1.0), (' which', 1.0), (' water', 1.0), (' changes', 1.0), (' from', 1.0), (' a', 1.0), (' liquid', 1.0), (' to', 1.0), (' a', 1.0), (' gas', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0)]</t>
+          <t>[('?\n', 1.0), ('The', 0.6514), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.\n', 0.5), ('Q', 1.0), (':', 1.0), (' What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('??', 1.0), ('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0)]</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -5791,24 +5999,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>What is the boiling point of water in Celsius? The boiling point of water is 100 degrees Celsius. The boiling point of water is 212 degrees Fahrenheit. The boiling point of water is 373</t>
+          <t>What is the boiling point of water in Celsius???
+What is the boiling point of water in Celsius???
+The boiling point of water is 100 degrees Celsius.
+The boiling point of water is</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.5</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9771599769592285</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3465735912322998</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H141" t="b">
         <v>1</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[(' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.', 1.0), (' The', 0.5), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('212', 1.0), (' degrees', 1.0), (' Fahrenheit', 1.0), ('.', 1.0), (' The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('373', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' in', 1.0), (' Celsius', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0), ('100', 1.0), (' degrees', 1.0), (' Celsius', 1.0), ('.\n', 0.5), ('The', 1.0), (' boiling', 1.0), (' point', 1.0), (' of', 1.0), (' water', 1.0), (' is', 1.0), (' ', 1.0)]</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -5829,28 +6040,29 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the last 2 weeks and I have been working on it for 12 hours a day. I have</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>0.06775045394897461</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0.9141772389411926</v>
       </c>
       <c r="G142" t="n">
-        <v>-0</v>
+        <v>1.256339192390442</v>
       </c>
       <c r="H142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' last', 0.3486), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' have', 0.5), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('12', 1.0), (' hours', 1.0), (' a', 1.0), (' day', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0)]</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -5867,28 +6079,29 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the last 2 weeks and I have been working on it for 12 hours a day. I have</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0.06775045394897461</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0.9141772389411926</v>
       </c>
       <c r="G143" t="n">
-        <v>-0</v>
+        <v>1.256339192390442</v>
       </c>
       <c r="H143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' last', 0.3486), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' have', 0.5), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('12', 1.0), (' hours', 1.0), (' a', 1.0), (' day', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0)]</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5905,28 +6118,29 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the past 2 weeks and I am still not done. I have been working on it for 2</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0.9552400708198547</v>
       </c>
       <c r="G144" t="n">
-        <v>-0</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' past', 0.6514), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' am', 1.0), (' still', 1.0), (' not', 1.0), (' done', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('2', 1.0)]</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -5943,28 +6157,29 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for a client for the past 2 weeks. I have been working on it for 2 weeks and I</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.2470741271972656</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0.9544669985771179</v>
       </c>
       <c r="G145" t="n">
-        <v>-0</v>
+        <v>0.830375075340271</v>
       </c>
       <c r="H145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' a', 0.5), (' client', 1.0), (' for', 1.0), (' the', 1.0), (' past', 1.0), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('2', 0.6357), (' weeks', 1.0), (' and', 1.0), (' I', 1.0)]</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -5981,28 +6196,29 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the past 2 weeks and I am still not done. I have been working on it for 2</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0.9552400708198547</v>
       </c>
       <c r="G146" t="n">
-        <v>-0</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' past', 0.6514), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' am', 1.0), (' still', 1.0), (' not', 1.0), (' done', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('2', 1.0)]</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -6019,28 +6235,29 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for a client for the past 2 weeks. I have been working on it for 12 hours a day</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0.07078792899847031</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0.9155146479606628</v>
       </c>
       <c r="G147" t="n">
-        <v>-0</v>
+        <v>0.852577269077301</v>
       </c>
       <c r="H147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' a', 0.5), (' client', 1.0), (' for', 1.0), (' the', 1.0), (' past', 1.0), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('12', 0.1821), (' hours', 1.0), (' a', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6057,28 +6274,29 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the past 2 weeks and I am still not done. I have been working on it for 2</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0.9552400708198547</v>
       </c>
       <c r="G148" t="n">
-        <v>-0</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' past', 0.6514), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' am', 1.0), (' still', 1.0), (' not', 1.0), (' done', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('2', 1.0)]</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6095,28 +6313,29 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the past 2 weeks and I am still not done. I have been working on it for 2</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0.2531490325927734</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0.9552400708198547</v>
       </c>
       <c r="G149" t="n">
-        <v>-0</v>
+        <v>0.8216341733932495</v>
       </c>
       <c r="H149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' past', 0.6514), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' am', 1.0), (' still', 1.0), (' not', 1.0), (' done', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('2', 1.0)]</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6133,28 +6352,29 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for a client for the past 2 weeks. I have been working on it for 10 hours a day</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0.07078792899847031</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0.9155146479606628</v>
       </c>
       <c r="G150" t="n">
-        <v>-0</v>
+        <v>0.852577269077301</v>
       </c>
       <c r="H150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' a', 0.5), (' client', 1.0), (' for', 1.0), (' the', 1.0), (' past', 1.0), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('10', 0.1821), (' hours', 1.0), (' a', 1.0), (' day', 1.0)]</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -6171,28 +6391,29 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>How many hours are there in a day? 24? 48? 72? 96? 120? 144? 168? 192? 216? 240?</t>
+          <t>How many hours are there in a day???
+I have been working on a project for the last 2 weeks and I am still not done. I have been working on it for 2</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.06775045394897461</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0.9141772389411926</v>
       </c>
       <c r="G151" t="n">
-        <v>-0</v>
+        <v>1.256339192390442</v>
       </c>
       <c r="H151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[(' ', 1.0), ('24', 1.0), ('?', 1.0), (' ', 1.0), ('48', 1.0), ('?', 1.0), (' ', 1.0), ('72', 1.0), ('?', 1.0), (' ', 1.0), ('96', 1.0), ('?', 1.0), (' ', 1.0), ('120', 1.0), ('?', 1.0), (' ', 1.0), ('144', 1.0), ('?', 1.0), (' ', 1.0), ('168', 1.0), ('?', 1.0), (' ', 1.0), ('192', 1.0), ('?', 1.0), (' ', 1.0), ('216', 1.0), ('?', 1.0), (' ', 1.0), ('240', 1.0), ('?', 1.0)]</t>
+          <t>[('?\n', 1.0), ('I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' a', 0.7773), (' project', 1.0), (' for', 1.0), (' the', 0.5), (' last', 0.3486), (' ', 1.0), ('2', 1.0), (' weeks', 1.0), (' and', 1.0), (' I', 1.0), (' am', 0.5), (' still', 1.0), (' not', 1.0), (' done', 1.0), ('.', 1.0), (' I', 1.0), (' have', 1.0), (' been', 1.0), (' working', 1.0), (' on', 1.0), (' it', 1.0), (' for', 1.0), (' ', 1.0), ('2', 1.0)]</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6209,29 +6430,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a Portuguese speaking country. The official language of Brazil is Portuguese. The Portuguese language is the</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G152" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H152" t="b">
         <v>1</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' Portuguese', 0.5), (' speaking', 1.0), (' country', 1.0), ('.', 1.0), (' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="153">
@@ -6248,29 +6470,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a country in South America. The official language of Brazil is Portuguese. Portuguese is the most</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.02783751860260963</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0.8874713778495789</v>
       </c>
       <c r="G153" t="n">
-        <v>-0</v>
+        <v>1.374200582504272</v>
       </c>
       <c r="H153" t="b">
         <v>1</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' country', 0.5), (' in', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' The', 0.5), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' Portuguese', 0.2227), (' is', 1.0), (' the', 1.0), (' most', 0.5)]</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="154">
@@ -6287,29 +6510,30 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a country in South America. It is the largest country in South America and the fifth largest</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.9548416137695312</v>
       </c>
       <c r="G154" t="n">
-        <v>-0</v>
+        <v>0.6931471824645996</v>
       </c>
       <c r="H154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' country', 0.5), (' in', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' It', 0.5), (' is', 1.0), (' the', 1.0), (' largest', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' and', 1.0), (' the', 1.0), (' fifth', 1.0), (' largest', 1.0)]</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="155">
@@ -6326,29 +6550,30 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a Portuguese speaking country. The official language of Brazil is Portuguese. The Portuguese language is the</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G155" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H155" t="b">
         <v>1</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' Portuguese', 0.5), (' speaking', 1.0), (' country', 1.0), ('.', 1.0), (' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="156">
@@ -6365,29 +6590,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a Portuguese speaking country. The official language of Brazil is Portuguese. The Portuguese language is the</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G156" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H156" t="b">
         <v>1</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' Portuguese', 0.5), (' speaking', 1.0), (' country', 1.0), ('.', 1.0), (' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="157">
@@ -6404,29 +6630,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a Portuguese speaking country. The official language of Brazil is Portuguese. The Portuguese language is the</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G157" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H157" t="b">
         <v>1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' Portuguese', 0.5), (' speaking', 1.0), (' country', 1.0), ('.', 1.0), (' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="158">
@@ -6443,29 +6670,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a country in South America. The official language of Brazil is Portuguese. Portuguese is the most</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0.02783751860260963</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0.8874713778495789</v>
       </c>
       <c r="G158" t="n">
-        <v>-0</v>
+        <v>1.374200582504272</v>
       </c>
       <c r="H158" t="b">
         <v>1</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' country', 0.5), (' in', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' The', 0.5), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' Portuguese', 0.2227), (' is', 1.0), (' the', 1.0), (' most', 0.5)]</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="159">
@@ -6482,29 +6710,30 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a Portuguese speaking country. The official language of Brazil is Portuguese. The Portuguese language is the</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G159" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H159" t="b">
         <v>1</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' Portuguese', 0.5), (' speaking', 1.0), (' country', 1.0), ('.', 1.0), (' The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 1.0), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="160">
@@ -6521,29 +6750,30 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a country in South America. The official language of Brazil is Portuguese. The Portuguese language is</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0.1943249702453613</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0.9468567371368408</v>
       </c>
       <c r="G160" t="n">
-        <v>-0</v>
+        <v>0.8889715671539307</v>
       </c>
       <c r="H160" t="b">
         <v>1</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' country', 0.5), (' in', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' The', 0.5), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 0.7773), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="161">
@@ -6560,29 +6790,30 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>What language is primarily spoken in Brazil? Portuguese. Brazil is the only Portuguese-speaking country in the Americas, and the only country in South America where Portuguese is the official language.
-What is the</t>
+          <t>What language is primarily spoken in Brazil???
+What language is primarily spoken in Brazil???
+Brazil is a country in South America. The official language of Brazil is Portuguese. The Portuguese language is</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.1943249702453613</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0.9468567371368408</v>
       </c>
       <c r="G161" t="n">
-        <v>-0</v>
+        <v>0.8889715671539307</v>
       </c>
       <c r="H161" t="b">
         <v>1</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[(' Portuguese', 1.0), ('.', 1.0), (' Brazil', 1.0), (' is', 1.0), (' the', 1.0), (' only', 1.0), (' Portuguese', 1.0), ('-speaking', 1.0), (' country', 1.0), (' in', 1.0), (' the', 1.0), (' Americas', 1.0), (',', 1.0), (' and', 1.0), (' the', 1.0), (' only', 1.0), (' country', 1.0), (' in', 1.0), (' South', 1.0), (' America', 1.0), (' where', 1.0), (' Portuguese', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), ('.\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' language', 1.0), (' is', 1.0), (' primarily', 1.0), (' spoken', 1.0), (' in', 1.0), (' Brazil', 1.0), ('??', 1.0), ('?\n', 1.0), ('Brazil', 1.0), (' is', 1.0), (' a', 1.0), (' country', 0.5), (' in', 1.0), (' South', 1.0), (' America', 1.0), ('.', 1.0), (' The', 0.5), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Brazil', 1.0), (' is', 1.0), (' Portuguese', 1.0), ('.', 1.0), (' The', 0.7773), (' Portuguese', 1.0), (' language', 1.0), (' is', 1.0)]</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="162">
@@ -6599,24 +6830,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is the most widely spoken language in Europe. German is also the most widely spoken mother tongue in the</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0.1111111044883728</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0.9293769598007202</v>
       </c>
       <c r="G162" t="n">
-        <v>-0</v>
+        <v>0.7324082255363464</v>
       </c>
       <c r="H162" t="b">
         <v>1</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.3333), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' mother', 0.3333), (' tongue', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -6637,24 +6869,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is the most widely spoken language in Europe. German is also the most widely spoken language in the European</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0.1111111044883728</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0.9293769598007202</v>
       </c>
       <c r="G163" t="n">
-        <v>-0</v>
+        <v>0.7324082255363464</v>
       </c>
       <c r="H163" t="b">
         <v>1</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.3333), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 0.3333), (' in', 1.0), (' the', 1.0), (' European', 1.0)]</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -6675,24 +6908,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is the most widely spoken language in Europe. German is also the most widely spoken mother tongue in the</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>0.1111111044883728</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0.9293769598007202</v>
       </c>
       <c r="G164" t="n">
-        <v>-0</v>
+        <v>0.7324082255363464</v>
       </c>
       <c r="H164" t="b">
         <v>1</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.3333), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' mother', 0.3333), (' tongue', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -6713,24 +6947,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is the most widely spoken language in Europe. German is also the most widely spoken language in the European</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>0.1111111044883728</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0.9293769598007202</v>
       </c>
       <c r="G165" t="n">
-        <v>-0</v>
+        <v>0.7324082255363464</v>
       </c>
       <c r="H165" t="b">
         <v>1</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.3333), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 0.3333), (' in', 1.0), (' the', 1.0), (' European', 1.0)]</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -6751,24 +6986,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0.1666666567325592</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0.9420232772827148</v>
       </c>
       <c r="G166" t="n">
-        <v>-0</v>
+        <v>0.7127777338027954</v>
       </c>
       <c r="H166" t="b">
         <v>1</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 0.3333), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 0.5)]</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -6789,24 +7025,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is the most widely spoken language in Europe. German is also the most widely spoken mother tongue in the</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>0.1111111044883728</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0.9293769598007202</v>
       </c>
       <c r="G167" t="n">
-        <v>-0</v>
+        <v>0.7324082255363464</v>
       </c>
       <c r="H167" t="b">
         <v>1</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.3333), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' mother', 0.3333), (' tongue', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -6827,24 +7064,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is the most widely spoken language in Europe. German is also the most widely spoken mother tongue in the</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>0.1111111044883728</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0.9293769598007202</v>
       </c>
       <c r="G168" t="n">
-        <v>-0</v>
+        <v>0.7324082255363464</v>
       </c>
       <c r="H168" t="b">
         <v>1</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 0.3333), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' mother', 0.3333), (' tongue', 1.0), (' in', 1.0), (' the', 1.0)]</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -6865,24 +7103,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is also the most widely spoken language in Europe. German is the native language of about 95 million</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0.03035632893443108</v>
       </c>
       <c r="F169" t="n">
-        <v>1</v>
+        <v>0.890037477016449</v>
       </c>
       <c r="G169" t="n">
-        <v>-0</v>
+        <v>1.022956967353821</v>
       </c>
       <c r="H169" t="b">
         <v>1</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.3333), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 0.1821), (' native', 1.0), (' language', 1.0), (' of', 1.0), (' about', 0.5), (' ', 1.0), ('95', 1.0), (' million', 1.0)]</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -6903,24 +7142,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is also the most widely spoken language in Europe. German is the native language of about 95 million</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0.03035632893443108</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>0.890037477016449</v>
       </c>
       <c r="G170" t="n">
-        <v>-0</v>
+        <v>1.022956967353821</v>
       </c>
       <c r="H170" t="b">
         <v>1</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.3333), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' the', 0.1821), (' native', 1.0), (' language', 1.0), (' of', 1.0), (' about', 0.5), (' ', 1.0), ('95', 1.0), (' million', 1.0)]</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -6941,24 +7181,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Which language is spoken in Germany? German is the official language of Germany. It is spoken by 95% of the population. German is also the official language of Austria, Switzerland,</t>
+          <t>Which language is spoken in Germany???
+German is the official language of Germany. It is also the most widely spoken language in Europe. German is also the second most widely spoken language in</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>0.01517816074192524</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>0.8697090148925781</v>
       </c>
       <c r="G171" t="n">
-        <v>-0</v>
+        <v>1.369530558586121</v>
       </c>
       <c r="H171" t="b">
         <v>1</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[(' German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' spoken', 1.0), (' by', 1.0), (' ', 1.0), ('95', 1.0), ('%', 1.0), (' of', 1.0), (' the', 1.0), (' population', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Austria', 1.0), (',', 1.0), (' Switzerland', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('German', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' Germany', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' also', 0.3333), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' Europe', 1.0), ('.', 1.0), (' German', 1.0), (' is', 1.0), (' also', 0.1821), (' the', 0.5), (' second', 0.5), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0)]</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -6979,8 +7220,9 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -6997,7 +7239,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -7018,8 +7260,9 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -7036,7 +7279,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -7057,8 +7300,9 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -7075,7 +7319,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -7096,8 +7340,9 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -7114,7 +7359,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -7135,8 +7380,9 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -7153,7 +7399,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J176" t="n">
@@ -7174,8 +7420,9 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -7192,7 +7439,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -7213,8 +7460,9 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -7231,7 +7479,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -7252,8 +7500,9 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -7270,7 +7519,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J179" t="n">
@@ -7291,8 +7540,9 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -7309,7 +7559,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J180" t="n">
@@ -7330,8 +7580,9 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>What is the official language of China? What is the official language of China?
-The official language of China is Mandarin. Mandarin is the most widely spoken language in the world. It is the</t>
+          <t>What is the official language of China???
+What is the official language of China???
+The official language of China is Mandarin. It is the most widely spoken language in the world. It</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -7348,7 +7599,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[(' What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' Mandarin', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' official', 1.0), (' language', 1.0), (' of', 1.0), (' China', 1.0), (' is', 1.0), (' Mandarin', 1.0), ('.', 1.0), (' It', 1.0), (' is', 1.0), (' the', 1.0), (' most', 1.0), (' widely', 1.0), (' spoken', 1.0), (' language', 1.0), (' in', 1.0), (' the', 1.0), (' world', 1.0), ('.', 1.0), (' It', 1.0)]</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -7369,24 +7620,26 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California, that designs, develops, and sells consumer electronics, computer software, and online</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F182" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G182" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H182" t="b">
         <v>1</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0), (' that', 1.0), (' designs', 1.0), (',', 1.0), (' develops', 1.0), (',', 1.0), (' and', 1.0), (' sells', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' online', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -7407,27 +7660,26 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone is a smartphone developed by Apple Inc. It was first released on June</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>0.2270916998386383</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F183" t="n">
-        <v>0.9517875909805298</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G183" t="n">
-        <v>0.6466038227081299</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H183" t="b">
         <v>1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' It', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J183" t="n">
@@ -7448,28 +7700,26 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.424263209104538</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F184" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G184" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H184" t="b">
         <v>1</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J184" t="n">
@@ -7490,27 +7740,26 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-The iPhone is a smartphone developed by Apple Inc. It was first released on June</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.2270916998386383</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F185" t="n">
-        <v>0.9517875909805298</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G185" t="n">
-        <v>0.6466038227081299</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H185" t="b">
         <v>1</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('The', 0.3486), (' iPhone', 1.0), (' is', 1.0), (' a', 1.0), (' smartphone', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' It', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -7531,24 +7780,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California, that designs, develops, and sells consumer electronics, computer software, and online</t>
+          <t>Which company developed the iPhone???
+Apple Inc. is an American multinational corporation that designs and markets consumer electronics, computer software, and personal computers. The company's best-known hardware products</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.2227001488208771</v>
       </c>
       <c r="F186" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9511682391166687</v>
       </c>
       <c r="G186" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.334479808807373</v>
       </c>
       <c r="H186" t="b">
         <v>1</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0), (' that', 1.0), (' designs', 1.0), (',', 1.0), (' develops', 1.0), (',', 1.0), (' and', 1.0), (' sells', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' online', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Apple', 0.2227), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' corporation', 1.0), (' that', 1.0), (' designs', 1.0), (' and', 1.0), (' markets', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' personal', 1.0), (' computers', 1.0), ('.', 1.0), (' The', 1.0), (' company', 1.0), ("'s", 1.0), (' best', 1.0), ('-known', 1.0), (' hardware', 1.0), (' products', 1.0)]</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -7569,28 +7819,26 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0.424263209104538</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F187" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G187" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H187" t="b">
         <v>1</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -7611,28 +7859,26 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>0.424263209104538</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F188" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G188" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H188" t="b">
         <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -7653,28 +7899,26 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0.424263209104538</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F189" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G189" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H189" t="b">
         <v>1</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -7695,28 +7939,26 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple
-Which company developed the iPhone?
-Apple developed the iPhone.
-What is the name of the company that developed the iPhone?
-The company that developed the</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.424263209104538</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F190" t="n">
-        <v>0.9718245267868042</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G190" t="n">
-        <v>0.5584724545478821</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H190" t="b">
         <v>1</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), ('\n', 0.6514), ('Which', 1.0), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('Apple', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('.\n', 1.0), ('What', 0.6514), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('?\n', 1.0), ('The', 1.0), (' company', 1.0), (' that', 1.0), (' developed', 1.0), (' the', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -7737,24 +7979,26 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Which company developed the iPhone? Apple Inc. is an American multinational technology company headquartered in Cupertino, California, that designs, develops, and sells consumer electronics, computer software, and online</t>
+          <t>Which company developed the iPhone???
+Which company developed the iPhone???
+The iPhone was developed by Apple Inc. The iPhone was first released on June 29, 2007.</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>0.3486451208591461</v>
+        <v>0.7772998809814453</v>
       </c>
       <c r="F191" t="n">
-        <v>0.9654862880706787</v>
+        <v>0.9916375279426575</v>
       </c>
       <c r="G191" t="n">
-        <v>0.3673676252365112</v>
+        <v>0.1958244144916534</v>
       </c>
       <c r="H191" t="b">
         <v>1</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[(' Apple', 1.0), (' Inc', 0.3486), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' headquartered', 1.0), (' in', 1.0), (' Cupertino', 1.0), (',', 1.0), (' California', 1.0), (',', 1.0), (' that', 1.0), (' designs', 1.0), (',', 1.0), (' develops', 1.0), (',', 1.0), (' and', 1.0), (' sells', 1.0), (' consumer', 1.0), (' electronics', 1.0), (',', 1.0), (' computer', 1.0), (' software', 1.0), (',', 1.0), (' and', 1.0), (' online', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 0.7773), (' company', 1.0), (' developed', 1.0), (' the', 1.0), (' iPhone', 1.0), ('??', 1.0), ('?\n', 1.0), ('The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' developed', 1.0), (' by', 1.0), (' Apple', 1.0), (' Inc', 1.0), ('.', 1.0), (' The', 1.0), (' iPhone', 1.0), (' was', 1.0), (' first', 1.0), (' released', 1.0), (' on', 1.0), (' June', 1.0), (' ', 1.0), ('29', 1.0), (',', 1.0), (' ', 1.0), ('200', 1.0), ('7', 1.0), ('.', 1.0)]</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -7775,30 +8019,30 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos??</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G192" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 0.5), ('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="193">
@@ -7815,30 +8059,31 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
+          <t>What is the name of the online retailer founded by Jeff Bezos???
 What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+What is the name of the online retailer founded by Jeff Bezos?
+What</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G193" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('What', 1.0)]</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="194">
@@ -7855,30 +8100,30 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos??</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G194" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 0.5), ('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="195">
@@ -7895,30 +8140,30 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos??</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0.1743225604295731</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>0.9434345960617065</v>
       </c>
       <c r="G195" t="n">
-        <v>-0</v>
+        <v>0.713941216468811</v>
       </c>
       <c r="H195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 0.5), ('?\n', 1.0), ('What', 0.3486), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 1.0)]</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="196">
@@ -7935,30 +8180,31 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
+          <t>What is the name of the online retailer founded by Jeff Bezos???
 What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+What is the name of the online retailer founded by Jeff Bezos?
+What</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G196" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('What', 1.0)]</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="197">
@@ -7975,30 +8221,30 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American multinational technology company based in Seattle</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G197" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H197" t="b">
         <v>1</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 0.5), ('?\n', 1.0), ('Amazon', 0.6514), ('.com', 1.0), (',', 1.0), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0)]</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="198">
@@ -8015,30 +8261,30 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
-What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+          <t>What is the name of the online retailer founded by Jeff Bezos???
+What is the name of the online retailer founded by Jeff Bezos???
+Amazon.com, Inc. is an American multinational technology company based in Seattle</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0.3256774246692657</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0.9632956385612488</v>
       </c>
       <c r="G198" t="n">
-        <v>-0</v>
+        <v>0.6258097887039185</v>
       </c>
       <c r="H198" t="b">
         <v>1</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('??', 0.5), ('?\n', 1.0), ('Amazon', 0.6514), ('.com', 1.0), (',', 1.0), (' Inc', 1.0), ('.', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0)]</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="199">
@@ -8055,30 +8301,31 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
+          <t>What is the name of the online retailer founded by Jeff Bezos???
 What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+What is the name of the online retailer founded by Jeff Bezos?
+What</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G199" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('What', 1.0)]</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="200">
@@ -8095,30 +8342,31 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
+          <t>What is the name of the online retailer founded by Jeff Bezos???
 What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+What is the name of the online retailer founded by Jeff Bezos?
+What</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G200" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('What', 1.0)]</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="201">
@@ -8135,30 +8383,31 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>What is the name of the online retailer founded by Jeff Bezos? Amazon
+          <t>What is the name of the online retailer founded by Jeff Bezos???
 What is the name of the online retailer founded by Jeff Bezos?
-Amazon is an American electronic commerce and cloud computing company based in Seattle,</t>
+What is the name of the online retailer founded by Jeff Bezos?
+What</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0.9771599769592285</v>
       </c>
       <c r="G201" t="n">
-        <v>-0</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="H201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[(' Amazon', 1.0), ('\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('Amazon', 1.0), (' is', 1.0), (' an', 1.0), (' American', 1.0), (' electronic', 1.0), (' commerce', 1.0), (' and', 1.0), (' cloud', 1.0), (' computing', 1.0), (' company', 1.0), (' based', 1.0), (' in', 1.0), (' Seattle', 1.0), (',', 1.0)]</t>
+          <t>[('?\n', 1.0), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 0.5), ('What', 1.0), (' is', 1.0), (' the', 1.0), (' name', 1.0), (' of', 1.0), (' the', 1.0), (' online', 1.0), (' retailer', 1.0), (' founded', 1.0), (' by', 1.0), (' Jeff', 1.0), (' Be', 1.0), ('zos', 1.0), ('?\n', 1.0), ('What', 1.0)]</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="202">
@@ -8175,10 +8424,9 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -8195,7 +8443,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -8216,10 +8464,9 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -8236,7 +8483,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J203" t="n">
@@ -8257,10 +8504,9 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -8277,7 +8523,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -8298,10 +8544,9 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -8318,7 +8563,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -8339,10 +8584,9 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -8359,7 +8603,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -8380,10 +8624,9 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -8400,7 +8643,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -8421,10 +8664,9 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -8441,7 +8683,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -8462,10 +8704,9 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -8482,7 +8723,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -8503,10 +8744,9 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -8523,7 +8763,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -8544,10 +8784,9 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its search engine? Google
-Which company is known for its</t>
+          <t>Which company is known for its search engine???
+Which company is known for its search engine???
+Google is a multinational technology company that specializes in Internet-related services and products, which include online advertising</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -8564,7 +8803,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>[(' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('?', 1.0), (' Google', 1.0), ('\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0)]</t>
+          <t>[('?\n', 1.0), ('Which', 1.0), (' company', 1.0), (' is', 1.0), (' known', 1.0), (' for', 1.0), (' its', 1.0), (' search', 1.0), (' engine', 1.0), ('??', 1.0), ('?\n', 1.0), ('Google', 1.0), (' is', 1.0), (' a', 1.0), (' multinational', 1.0), (' technology', 1.0), (' company', 1.0), (' that', 1.0), (' specializes', 1.0), (' in', 1.0), (' Internet', 1.0), ('-related', 1.0), (' services', 1.0), (' and', 1.0), (' products', 1.0), (',', 1.0), (' which', 1.0), (' include', 1.0), (' online', 1.0), (' advertising', 1.0)]</t>
         </is>
       </c>
       <c r="J211" t="n">
